--- a/data/trans_orig/P25D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620609</t>
+          <t>620972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632290</t>
+          <t>632291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>669837</t>
+          <t>669714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>673574</t>
+          <t>673575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1293746</t>
+          <t>1292506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1305128</t>
+          <t>1304730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1175263</t>
+          <t>1175630</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1190673</t>
+          <t>1190385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>939599</t>
+          <t>939143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>953601</t>
+          <t>953408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2121916</t>
+          <t>2122232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2142039</t>
+          <t>2141716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24323</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31623</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>680193</t>
+          <t>680067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701570</t>
+          <t>701181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>917935</t>
+          <t>917782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>930994</t>
+          <t>931170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1606258</t>
+          <t>1605846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1629697</t>
+          <t>1629996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891201</t>
+          <t>891207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910333</t>
+          <t>910324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1079325</t>
+          <t>1079486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1087257</t>
+          <t>1087634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1974243</t>
+          <t>1975115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1995086</t>
+          <t>1995644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3393171</t>
+          <t>3392381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3426468</t>
+          <t>3426746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3620078</t>
+          <t>3619224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3640035</t>
+          <t>3640210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7023108</t>
+          <t>7024272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7061281</t>
+          <t>7061674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -775,17 +775,17 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>628872</t>
+          <t>683785</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620972</t>
+          <t>675334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632291</t>
+          <t>687314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>672487</t>
+          <t>729527</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>669714</t>
+          <t>726827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>673575</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1301359</t>
+          <t>1413312</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292506</t>
+          <t>1404455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304730</t>
+          <t>1417333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633158</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633158</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633158</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1307109</t>
+          <t>1419432</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1307109</t>
+          <t>1419432</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1307109</t>
+          <t>1419432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1185064</t>
+          <t>1040517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1175630</t>
+          <t>1031690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1190385</t>
+          <t>1045802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>948795</t>
+          <t>1061184</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>939143</t>
+          <t>1051229</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>953408</t>
+          <t>1065720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2133859</t>
+          <t>2101701</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2122232</t>
+          <t>2090313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2141716</t>
+          <t>2108718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957527</t>
+          <t>1070150</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957527</t>
+          <t>1070150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957527</t>
+          <t>1070150</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150391</t>
+          <t>2119067</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150391</t>
+          <t>2119067</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150391</t>
+          <t>2119067</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>695908</t>
+          <t>792537</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>680067</t>
+          <t>778730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701181</t>
+          <t>798224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>926335</t>
+          <t>804176</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>917782</t>
+          <t>796530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>931170</t>
+          <t>809531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1622241</t>
+          <t>1596713</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1605846</t>
+          <t>1581629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1629996</t>
+          <t>1604757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>903044</t>
+          <t>962517</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891207</t>
+          <t>947326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910324</t>
+          <t>970893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1084153</t>
+          <t>1107239</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1079486</t>
+          <t>1101572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1087634</t>
+          <t>1110782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1987197</t>
+          <t>2069757</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1975115</t>
+          <t>2052934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1995644</t>
+          <t>2078986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>919761</t>
+          <t>982782</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>919761</t>
+          <t>982782</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>919761</t>
+          <t>982782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090666</t>
+          <t>1114597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090666</t>
+          <t>1114597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090666</t>
+          <t>1114597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010427</t>
+          <t>2097379</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010427</t>
+          <t>2097379</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010427</t>
+          <t>2097379</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>92172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3412888</t>
+          <t>3479357</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3392381</t>
+          <t>3459473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3426746</t>
+          <t>3493456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3631770</t>
+          <t>3702126</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3619224</t>
+          <t>3689029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3640210</t>
+          <t>3710324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7044657</t>
+          <t>7181482</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7024272</t>
+          <t>7157860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7061674</t>
+          <t>7199274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
